--- a/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.0.xlsx
+++ b/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D6185A-6648-444F-985E-BB6324877977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE04A555-0F5C-46B0-AE5A-53A40C66D669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
   <sheets>
     <sheet name="SIM" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="195">
   <si>
     <t>項目</t>
     <rPh sb="0" eb="2">
@@ -1478,27 +1478,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>清水グループ御中_LINEOA施策提案【SIM】（離脱防止＋サイトのLINEボタン＋サンクスLINE誘導）</t>
-  </si>
-  <si>
-    <t>応募</t>
-  </si>
-  <si>
     <t>サイトUU</t>
   </si>
   <si>
-    <t>CV①応募：LINEのリンクからの応募だけ。サンクスLINEで友だちになった方（応募済み）の応募は数えない</t>
-  </si>
-  <si>
     <t>うち広告</t>
   </si>
   <si>
     <t>応募（サイト・仮に）</t>
   </si>
   <si>
-    <t>サイトからの応募は与件に無いので、仮にUUの1.5%（月134件）</t>
-  </si>
-  <si>
     <t>1か月目</t>
   </si>
   <si>
@@ -1526,27 +1514,6 @@
     <t>離脱防止ポップアップ＝UU×表示65%×クリック12.5%×追加12.5%（定義テキストの係数）</t>
   </si>
   <si>
-    <t>サンクスLINE誘導＝応募×遷移80%×追加45%（定義テキストの係数）</t>
-  </si>
-  <si>
-    <t>サイトのLINEボタン（UUの0.5%・FMTの係数）＋離脱防止＋サンクスLINE誘導</t>
-  </si>
-  <si>
-    <t>ブロック率：求人は用が済むとブロックされやすいので、38%から少しずつ上がる想定</t>
-  </si>
-  <si>
-    <t>企画配信 月3回（業界資料の竹＝コンサル基本 月20万円は月3投稿。新着求人・職種ごとの案内）</t>
-  </si>
-  <si>
-    <t>ステップ配信3通（友だち追加の翌日以降。職種ごとに中身を分ける）</t>
-  </si>
-  <si>
-    <t>応募：クリックの0.3〜1.0%前後</t>
-  </si>
-  <si>
-    <t>離脱防止ポップアップ：初期1.5万円・月3万円</t>
-  </si>
-  <si>
     <t>サンクスLINE誘導</t>
   </si>
   <si>
@@ -1556,16 +1523,58 @@
     <t>アカウント費：FMTの式（開設3万円）</t>
   </si>
   <si>
-    <t>LINE運用コンサル（竹：コンサル基本）</t>
-  </si>
-  <si>
-    <t>LINE運用コンサル（竹：コンサル基本）月20万円。初期は初期30万円</t>
-  </si>
-  <si>
     <t>CV数（+LINEOA施策）</t>
   </si>
   <si>
-    <t>CV①_応募</t>
+    <t>株式会社横浜シミズ御中_LINEOA施策提案【SIM】（サイトのLINEボタン＋サンクスLINE誘導）</t>
+  </si>
+  <si>
+    <t>新規応募</t>
+  </si>
+  <si>
+    <t>CV①新規応募：サイトのLINEボタンで友だちになった方（応募前）が、配信から応募した数。サンクスLINE誘導で友だちになった方は応募済みなので、新規応募には数えない</t>
+  </si>
+  <si>
+    <t>再応募</t>
+  </si>
+  <si>
+    <t>サイトからの応募は与件に無いので、仮にUUの1.0%（月89件・資料と同じ）</t>
+  </si>
+  <si>
+    <t>サンクスLINE誘導＝応募×遷移80%×追加40%（資料と同じ・定義テキストの係数）</t>
+  </si>
+  <si>
+    <t>サイトのLINEボタン（UUの0.5%・FMTの係数）＋サンクスLINE誘導。離脱防止は入れていない</t>
+  </si>
+  <si>
+    <t>ブロック率：1か月目（E27）から、2か月目以降は前の月×1.025（式）</t>
+  </si>
+  <si>
+    <t>企画配信 月4回（週1回。次回イベントの募集・会場の案内）</t>
+  </si>
+  <si>
+    <t>ステップ配信は入れていない（資料に無いため）</t>
+  </si>
+  <si>
+    <t>新規応募：合計CVでクリックの0.3〜1.0%前後になるように置く</t>
+  </si>
+  <si>
+    <t>再応募：一度勤務した方が、次回イベントの募集から勤務希望を出した数（応募→勤務を経てからなので4か月目から）</t>
+  </si>
+  <si>
+    <t>離脱防止ポップアップ：入れていない（入れる場合 初期1.5万円・月3万円）</t>
+  </si>
+  <si>
+    <t>LINE運用（運用代行・効率改善）</t>
+  </si>
+  <si>
+    <t>LINE運用：資料の金額（初期構築10万円・月10万円）</t>
+  </si>
+  <si>
+    <t>CV①_新規応募</t>
+  </si>
+  <si>
+    <t>CV③_再応募</t>
   </si>
 </sst>
 </file>
@@ -2066,7 +2075,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2492,10 +2501,40 @@
     <xf numFmtId="14" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2519,44 +2558,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2943,7 +2949,7 @@
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">株式会社横浜シミズ御中_LINEOA施策提案【SIM】（サイトのLINEボタン＋サンクスLINE誘導）</t>
+          <t xml:space="preserve">株式会社横浜シミズ御中_LINEOA施策提案【SIM】（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導）</t>
         </is>
       </c>
       <c r="N4" s="55"/>
@@ -3008,22 +3014,20 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="147" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">新規応募</t>
-        </is>
+      <c r="C8" s="19" t="s">
+        <v>179</v>
       </c>
       <c r="D8" s="33">
         <v>0</v>
       </c>
       <c r="G8" s="121" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H8" s="122">
         <v>8947</v>
@@ -3035,17 +3039,15 @@
       <c r="K8" s="129">
         <v>0</v>
       </c>
-      <c r="N8" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CV①新規応募：サイトのLINEボタンで友だちになった方（応募前）が、配信から応募した数。サンクスLINE誘導で友だちになった方は応募済みなので、新規応募には数えない</t>
-        </is>
+      <c r="N8" s="69" t="s">
+        <v>180</v>
       </c>
       <c r="O8" s="35" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="138"/>
+      <c r="A9" s="148"/>
       <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
@@ -3056,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="124" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H9" s="125">
         <v>0</v>
@@ -3075,22 +3077,20 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="147" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">再応募</t>
-        </is>
+      <c r="C10" s="19" t="s">
+        <v>181</v>
       </c>
       <c r="D10" s="33">
         <v>0</v>
       </c>
       <c r="G10" s="124" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H10" s="125">
         <v>89</v>
@@ -3100,14 +3100,12 @@
       </c>
       <c r="J10" s="29"/>
       <c r="K10" s="118"/>
-      <c r="N10" s="132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトからの応募は与件に無いので、仮にUUの1.0%（月89件・資料と同じ）</t>
-        </is>
+      <c r="N10" s="132" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="138"/>
+      <c r="A11" s="148"/>
       <c r="B11" s="19" t="s">
         <v>10</v>
       </c>
@@ -3141,31 +3139,31 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="139"/>
+      <c r="A13" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="149"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="F13" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="I13" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="J13" s="36" t="s">
         <v>170</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="H13" s="36" t="s">
-        <v>172</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>174</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>1</v>
@@ -3187,7 +3185,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="150" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -3218,11 +3216,11 @@
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
       <c r="N14" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="141"/>
+      <c r="A15" s="151"/>
       <c r="B15" s="20" t="s">
         <v>34</v>
       </c>
@@ -3264,7 +3262,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="142"/>
+      <c r="A16" s="152"/>
       <c r="B16" s="20" t="s">
         <v>151</v>
       </c>
@@ -3306,7 +3304,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="140" t="s">
+      <c r="A17" s="150" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -3351,31 +3349,31 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="141"/>
+      <c r="A18" s="151"/>
       <c r="B18" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C18" s="100"/>
       <c r="D18" s="58" t="b">
         <v>0</v>
       </c>
       <c r="E18" s="57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>21</v>
@@ -3415,7 +3413,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141"/>
+      <c r="A19" s="151"/>
       <c r="B19" s="8" t="s">
         <v>114</v>
       </c>
@@ -3475,7 +3473,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="141"/>
+      <c r="A20" s="151"/>
       <c r="B20" s="8" t="s">
         <v>112</v>
       </c>
@@ -3510,7 +3508,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="142"/>
+      <c r="A21" s="152"/>
       <c r="B21" s="8" t="s">
         <v>113</v>
       </c>
@@ -3553,7 +3551,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="153" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3599,9 +3597,9 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="141"/>
+      <c r="A23" s="151"/>
       <c r="B23" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="44" t="s">
@@ -3628,7 +3626,7 @@
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
       <c r="N23" s="69" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="O23" s="17" t="s">
         <v>41</v>
@@ -3646,7 +3644,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="141"/>
+      <c r="A24" s="151"/>
       <c r="B24" s="6" t="s">
         <v>114</v>
       </c>
@@ -3655,29 +3653,27 @@
         <v>20</v>
       </c>
       <c r="E24" s="46">
-        <f>IF(E19=FALSE,0,E16*0.8*0.4)</f>
+        <f t="shared" ref="E24:J24" si="4">IF(E19=FALSE,0,E16*0.8*0.4)</f>
       </c>
       <c r="F24" s="63">
-        <f>IF(F19=FALSE,0,F16*0.8*0.4)</f>
+        <f t="shared" si="4"/>
       </c>
       <c r="G24" s="63">
-        <f>IF(G19=FALSE,0,G16*0.8*0.4)</f>
+        <f t="shared" si="4"/>
       </c>
       <c r="H24" s="63">
-        <f>IF(H19=FALSE,0,H16*0.8*0.4)</f>
+        <f t="shared" si="4"/>
       </c>
       <c r="I24" s="63">
-        <f>IF(I19=FALSE,0,I16*0.8*0.4)</f>
+        <f t="shared" si="4"/>
       </c>
       <c r="J24" s="63">
-        <f>IF(J19=FALSE,0,J16*0.8*0.4)</f>
+        <f t="shared" si="4"/>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
-      <c r="N24" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導＝応募×遷移80%×追加40%（資料と同じ・定義テキストの係数）</t>
-        </is>
+      <c r="N24" s="69" t="s">
+        <v>183</v>
       </c>
       <c r="O24" s="22" t="s">
         <v>43</v>
@@ -3695,7 +3691,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="142"/>
+      <c r="A25" s="152"/>
       <c r="B25" s="6" t="s">
         <v>67</v>
       </c>
@@ -3737,10 +3733,10 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="145"/>
+      <c r="B26" s="138"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>20</v>
@@ -3767,7 +3763,7 @@
       <c r="L26" s="7"/>
       <c r="N26" s="72" t="inlineStr">
         <is>
-          <t xml:space="preserve">サイトのLINEボタン（UUの0.5%・FMTの係数）＋サンクスLINE誘導。離脱防止は入れていない</t>
+          <t xml:space="preserve">サイトのLINEボタン（UUの0.5%・FMTの係数）＋離脱防止ポップアップ＋サンクスLINE誘導</t>
         </is>
       </c>
       <c r="O26" s="17" t="s">
@@ -3783,10 +3779,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="145"/>
+      <c r="B27" s="138"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0</v>
@@ -3811,10 +3807,8 @@
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ブロック率：1か月目（E27）から、2か月目以降は前の月×1.025（式）</t>
-        </is>
+      <c r="N27" t="s">
+        <v>185</v>
       </c>
       <c r="O27" s="17" t="s">
         <v>41</v>
@@ -3832,10 +3826,10 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="146" t="s">
+      <c r="A28" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="147"/>
+      <c r="B28" s="155"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>0</v>
@@ -3876,10 +3870,10 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="149"/>
+      <c r="B29" s="144"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
@@ -3914,10 +3908,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="142"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -3942,10 +3936,8 @@
       </c>
       <c r="K30" s="11"/>
       <c r="L30" s="7"/>
-      <c r="N30" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">企画配信 月4回（週1回。次回イベントの募集・会場の案内）</t>
-        </is>
+      <c r="N30" s="69" t="s">
+        <v>186</v>
       </c>
       <c r="O30" s="17" t="s">
         <v>120</v>
@@ -3958,10 +3950,10 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="145"/>
+      <c r="B31" s="138"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
@@ -3993,37 +3985,37 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="141" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="136"/>
+      <c r="B32" s="142"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
       </c>
       <c r="E32" s="45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F32" s="45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G32" s="45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" s="45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I32" s="45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J32" s="45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
       <c r="N32" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">ステップ配信は入れていない（資料に無いため）</t>
+          <t xml:space="preserve">ステップ配信 4通（あいさつメッセージの後、友だち追加から14日以内）</t>
         </is>
       </c>
       <c r="O32" s="17" t="s">
@@ -4041,10 +4033,10 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="145"/>
+      <c r="B33" s="138"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
@@ -4080,10 +4072,10 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="149"/>
+      <c r="B34" s="144"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
@@ -4119,10 +4111,10 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="149"/>
+      <c r="B35" s="144"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
@@ -4158,7 +4150,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="145" t="s">
         <v>5</v>
       </c>
       <c r="B36" s="6">
@@ -4190,10 +4182,8 @@
         <f>SUM(E36:J36)</f>
       </c>
       <c r="L36" s="7"/>
-      <c r="N36" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">新規応募：合計CVでクリックの0.3〜1.0%前後になるように置く</t>
-        </is>
+      <c r="N36" s="69" t="s">
+        <v>188</v>
       </c>
       <c r="O36" s="17" t="s">
         <v>126</v>
@@ -4204,7 +4194,7 @@
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="151"/>
+      <c r="A37" s="146"/>
       <c r="B37" s="6">
         <f>+C9</f>
       </c>
@@ -4239,7 +4229,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="145" t="s">
         <v>8</v>
       </c>
       <c r="B38" s="6">
@@ -4271,17 +4261,15 @@
         <f>SUM(E38:J38)</f>
       </c>
       <c r="L38" s="7"/>
-      <c r="N38" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">再応募：一度勤務した方が、次回イベントの募集から勤務希望を出した数（応募→勤務を経てからなので4か月目から）</t>
-        </is>
+      <c r="N38" s="69" t="s">
+        <v>189</v>
       </c>
       <c r="O38" s="21" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="151"/>
+      <c r="A39" s="146"/>
       <c r="B39" s="6">
         <f>+C11</f>
       </c>
@@ -4319,10 +4307,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="153"/>
+      <c r="B40" s="140"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="13">+SUM(D36:D39)</f>
@@ -4402,10 +4390,10 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="145"/>
+      <c r="B44" s="138"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>21</v>
@@ -4432,10 +4420,10 @@
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="137" t="s">
         <v>131</v>
       </c>
-      <c r="B45" s="145"/>
+      <c r="B45" s="138"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
       </c>
@@ -4464,10 +4452,10 @@
       <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="144" t="s">
+      <c r="A46" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="145"/>
+      <c r="B46" s="138"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>21</v>
@@ -4494,10 +4482,10 @@
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="144" t="s">
+      <c r="A47" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="145"/>
+      <c r="B47" s="138"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>21</v>
@@ -4524,10 +4512,10 @@
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="144" t="s">
+      <c r="A48" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="138"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>21</v>
@@ -4554,10 +4542,10 @@
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="152" t="s">
+      <c r="A49" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="B49" s="153"/>
+      <c r="B49" s="140"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>21</v>
@@ -4584,10 +4572,10 @@
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="153"/>
+      <c r="B50" s="140"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>21</v>
@@ -4614,10 +4602,10 @@
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="154" t="s">
+      <c r="A51" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="B51" s="155"/>
+      <c r="B51" s="136"/>
       <c r="C51" s="110">
         <f>+C45</f>
       </c>
@@ -4663,10 +4651,10 @@
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="B54" s="145"/>
+      <c r="B54" s="138"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
@@ -4693,10 +4681,10 @@
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="137" t="s">
         <v>131</v>
       </c>
-      <c r="B55" s="145"/>
+      <c r="B55" s="138"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
@@ -4723,10 +4711,10 @@
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B56" s="145"/>
+      <c r="B56" s="138"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>21</v>
@@ -4753,10 +4741,10 @@
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="144" t="s">
+      <c r="A57" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="145"/>
+      <c r="B57" s="138"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>21</v>
@@ -4783,10 +4771,10 @@
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="144" t="s">
+      <c r="A58" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="B58" s="145"/>
+      <c r="B58" s="138"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>21</v>
@@ -4813,10 +4801,10 @@
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="153"/>
+      <c r="B59" s="140"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
@@ -4841,10 +4829,10 @@
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="153"/>
+      <c r="B60" s="140"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -4857,10 +4845,10 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="154" t="s">
+      <c r="A61" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="155"/>
+      <c r="B61" s="136"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
@@ -4932,41 +4920,41 @@
         <v>49</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C66" s="90">
         <v>0</v>
       </c>
       <c r="D66" s="51">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E66" s="28">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="F66" s="28">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="G66" s="28">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="H66" s="28">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I66" s="28">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="J66" s="28">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="N66" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">離脱防止ポップアップ：入れていない（入れる場合 初期1.5万円・月3万円）</t>
+          <t xml:space="preserve">離脱防止ポップアップ：初期1.5万円・月3万円</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="6" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C67" s="90">
         <v>0</v>
@@ -4993,7 +4981,7 @@
         <v>30000</v>
       </c>
       <c r="N67" s="69" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5026,7 +5014,7 @@
         <f t="shared" si="31"/>
       </c>
       <c r="N68" s="69" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="O68" s="17" t="s">
         <v>130</v>
@@ -5037,10 +5025,8 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="15"/>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINE運用（運用代行・効率改善）</t>
-        </is>
+      <c r="B69" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="C69" s="90">
         <v>0</v>
@@ -5066,10 +5052,8 @@
       <c r="J69" s="28">
         <v>100000</v>
       </c>
-      <c r="N69" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINE運用：資料の金額（初期構築10万円・月10万円）</t>
-        </is>
+      <c r="N69" s="69" t="s">
+        <v>192</v>
       </c>
       <c r="O69" s="5" t="s">
         <v>51</v>
@@ -5267,6 +5251,29 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
@@ -5279,29 +5286,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5352,14 +5336,17 @@
         <v>139</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86">
+      <c r="C4" s="86" t="str">
         <f>+SIM!D24</f>
+        <v>--</v>
       </c>
       <c r="D4" s="28">
         <f>+SIM!G51</f>
+        <v>135000</v>
       </c>
       <c r="E4" s="28">
         <f>+SIM!J51</f>
+        <v>135000</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5368,14 +5355,17 @@
         <v>140</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86">
+      <c r="C5" s="86" t="str">
         <f>+SIM!D25</f>
+        <v>--</v>
       </c>
       <c r="D5" s="28">
         <f>+SIM!G61</f>
+        <v>135000</v>
       </c>
       <c r="E5" s="28">
         <f>+SIM!J61</f>
+        <v>135000</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5386,12 +5376,15 @@
       <c r="B6" s="7"/>
       <c r="C6" s="117">
         <f>+SIM!D28</f>
+        <v>0</v>
       </c>
       <c r="D6" s="87">
         <f>+SIM!G28</f>
+        <v>492.24890625000006</v>
       </c>
       <c r="E6" s="87">
         <f>+SIM!J28</f>
+        <v>984.49781250000001</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -5402,12 +5395,15 @@
       <c r="B7" s="7"/>
       <c r="C7" s="88">
         <f>+SIM!D27</f>
+        <v>0</v>
       </c>
       <c r="D7" s="89">
         <f>+SIM!G27</f>
+        <v>0.33619999999999994</v>
       </c>
       <c r="E7" s="89">
         <f>+SIM!J27</f>
+        <v>0.36205062812499983</v>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -5418,12 +5414,15 @@
       <c r="B8" s="7"/>
       <c r="C8" s="117">
         <f>+SIM!D29</f>
+        <v>0</v>
       </c>
       <c r="D8" s="10">
         <f>+SIM!G29</f>
+        <v>326.75482396875009</v>
       </c>
       <c r="E8" s="10">
         <f>+SIM!J29</f>
+        <v>628.05976109668677</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -5442,12 +5441,15 @@
       <c r="B10" s="7"/>
       <c r="C10" s="117">
         <f>+SIM!D34</f>
+        <v>0</v>
       </c>
       <c r="D10" s="10">
         <f>+SIM!G34</f>
+        <v>1307.0192958750004</v>
       </c>
       <c r="E10" s="10">
         <f>+SIM!J34</f>
+        <v>2009.7912355093979</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -5458,12 +5460,15 @@
       <c r="B11" s="7"/>
       <c r="C11" s="117">
         <f>+SIM!D35</f>
+        <v>0</v>
       </c>
       <c r="D11" s="10">
         <f>+SIM!G35</f>
+        <v>313.04696112890952</v>
       </c>
       <c r="E11" s="10">
         <f>+SIM!J35</f>
+        <v>481.36935756448418</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -5474,12 +5479,15 @@
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
+        <v>431.24520203985747</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
+        <v>280.44992452997059</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -5490,12 +5498,15 @@
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
+        <v>431.24520203985747</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
+        <v>280.44992452997059</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -5512,17 +5523,20 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="85" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
         <f>+SIM!$H$10</f>
+        <v>89</v>
       </c>
       <c r="D15" s="87">
         <f>+SIM!$H$10</f>
+        <v>89</v>
       </c>
       <c r="E15" s="87">
         <f>+SIM!$H$10</f>
+        <v>89</v>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -5531,17 +5545,20 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="85" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>SUM(C17:C20)</f>
+        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>SUM(D17:D20)</f>
+        <v>1</v>
       </c>
       <c r="E16" s="87">
         <f>SUM(E17:E20)</f>
+        <v>2</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -5555,20 +5572,21 @@
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CV①_新規応募</t>
-        </is>
+      <c r="A17" s="85" t="s">
+        <v>193</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
         <f>+SIM!D36</f>
+        <v>0</v>
       </c>
       <c r="D17" s="87">
         <f>+SIM!G36</f>
+        <v>1</v>
       </c>
       <c r="E17" s="87">
         <f>+SIM!J36</f>
+        <v>1</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -5600,12 +5618,15 @@
       <c r="B18" s="7"/>
       <c r="C18" s="87">
         <f>+SIM!D37</f>
+        <v>0</v>
       </c>
       <c r="D18" s="87">
         <f>+SIM!G37</f>
+        <v>0</v>
       </c>
       <c r="E18" s="87">
         <f>+SIM!J37</f>
+        <v>0</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -5625,26 +5646,28 @@
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CV③_再応募</t>
-        </is>
+      <c r="A19" s="85" t="s">
+        <v>194</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
         <f>+SIM!D38</f>
+        <v>0</v>
       </c>
       <c r="D19" s="87">
         <f>+SIM!G38</f>
+        <v>0</v>
       </c>
       <c r="E19" s="87">
         <f>+SIM!J38</f>
+        <v>1</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -5660,12 +5683,15 @@
       <c r="B20" s="7"/>
       <c r="C20" s="87">
         <f>+SIM!D39</f>
+        <v>0</v>
       </c>
       <c r="D20" s="87">
         <f>+SIM!G39</f>
+        <v>0</v>
       </c>
       <c r="E20" s="87">
         <f>+SIM!J39</f>
+        <v>0</v>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -5692,14 +5718,17 @@
         <v>141</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90">
+      <c r="C22" s="90" t="str">
         <f>+IFERROR(C4/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
+        <v>135000</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
+        <v>67500</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -5713,14 +5742,17 @@
         <v>142</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90">
+      <c r="C23" s="90" t="str">
         <f>+IFERROR(C5/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
+        <v>135000</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
+        <v>67500</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -5749,12 +5781,15 @@
       <c r="B25" s="7"/>
       <c r="C25" s="10">
         <f>+SIM!E68+C29*C30</f>
+        <v>5000</v>
       </c>
       <c r="D25" s="10">
         <f>+SIM!G68+D29*D30</f>
+        <v>5000</v>
       </c>
       <c r="E25" s="10">
         <f>+SIM!J68+E29*E30</f>
+        <v>5000</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -5790,12 +5825,15 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
+        <v>0</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
+        <v>0</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -5810,12 +5848,15 @@
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>
@@ -6397,20 +6438,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6432,14 +6473,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -6453,4 +6486,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.0.xlsx
+++ b/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE04A555-0F5C-46B0-AE5A-53A40C66D669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46F9FA9-5A61-4A6E-8F93-68881B18DF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="SIM_比較" sheetId="2" r:id="rId2"/>
     <sheet name="SIM考え方" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1" calcId="191029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2947,10 +2947,8 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">株式会社横浜シミズ御中_LINEOA施策提案【SIM】（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導）</t>
-        </is>
+      <c r="A4" s="56" t="s">
+        <v>178</v>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -3194,24 +3192,31 @@
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
+        <v>8947</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
+        <v>8947</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
+        <v>8947</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
@@ -3227,24 +3232,31 @@
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
+        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
+        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
@@ -3269,24 +3281,31 @@
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
+        <v>89</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
+        <v>89</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
+        <v>89</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
+        <v>89</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
+        <v>89</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
+        <v>89</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
+        <v>89</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -3467,6 +3486,7 @@
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
@@ -3607,21 +3627,27 @@
       </c>
       <c r="E23" s="46">
         <f t="shared" ref="E23:J23" si="3">IF(E18=FALSE,0,E14*$P$18*0.125*0.125)</f>
+        <v>90.867968750000003</v>
       </c>
       <c r="F23" s="46">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="G23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="H23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="I23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="J23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
@@ -3654,21 +3680,27 @@
       </c>
       <c r="E24" s="46">
         <f t="shared" ref="E24:J24" si="4">IF(E19=FALSE,0,E16*0.8*0.4)</f>
+        <v>28.480000000000004</v>
       </c>
       <c r="F24" s="63">
         <f t="shared" si="4"/>
+        <v>28.480000000000004</v>
       </c>
       <c r="G24" s="63">
         <f t="shared" si="4"/>
+        <v>28.480000000000004</v>
       </c>
       <c r="H24" s="63">
         <f t="shared" si="4"/>
+        <v>28.480000000000004</v>
       </c>
       <c r="I24" s="63">
         <f t="shared" si="4"/>
+        <v>28.480000000000004</v>
       </c>
       <c r="J24" s="63">
         <f t="shared" si="4"/>
+        <v>28.480000000000004</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
@@ -3701,21 +3733,27 @@
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" ref="F25:J25" si="5">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="G25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="I25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="J25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
@@ -3743,28 +3781,32 @@
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
+        <v>164.08296875000002</v>
       </c>
       <c r="F26" s="46">
         <f t="shared" ref="F26:J26" si="6">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>164.08296875000002</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>164.08296875000002</v>
       </c>
       <c r="H26" s="46">
         <f t="shared" si="6"/>
+        <v>164.08296875000002</v>
       </c>
       <c r="I26" s="46">
         <f t="shared" si="6"/>
+        <v>164.08296875000002</v>
       </c>
       <c r="J26" s="46">
         <f t="shared" si="6"/>
+        <v>164.08296875000002</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
-      <c r="N26" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトのLINEボタン（UUの0.5%・FMTの係数）＋離脱防止ポップアップ＋サンクスLINE誘導</t>
-        </is>
+      <c r="N26" s="72" t="s">
+        <v>184</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>40</v>
@@ -3792,18 +3834,23 @@
       </c>
       <c r="F27" s="47">
         <f>+E$27*1.025</f>
+        <v>0.32799999999999996</v>
       </c>
       <c r="G27" s="47">
         <f>+F$27*1.025</f>
+        <v>0.33619999999999994</v>
       </c>
       <c r="H27" s="47">
         <f>+G$27*1.025</f>
+        <v>0.34460499999999994</v>
       </c>
       <c r="I27" s="47">
         <f>+H$27*1.025</f>
+        <v>0.35322012499999988</v>
       </c>
       <c r="J27" s="47">
         <f>+I$27*1.025</f>
+        <v>0.36205062812499983</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
@@ -3836,21 +3883,27 @@
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
+        <v>164.08296875000002</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" ref="F28:J28" si="7">+E28+F26</f>
+        <v>328.16593750000004</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="7"/>
+        <v>492.24890625000006</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="7"/>
+        <v>656.33187500000008</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="7"/>
+        <v>820.41484375000005</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="7"/>
+        <v>984.49781250000001</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -3877,24 +3930,31 @@
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
+        <v>111.57641875</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" ref="F29:J29" si="8">+F28*(1-F27)</f>
+        <v>220.52751000000004</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="8"/>
+        <v>326.75482396875009</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="8"/>
+        <v>430.15662921562512</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="8"/>
+        <v>530.62781008876971</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="8"/>
+        <v>628.05976109668677</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -3957,24 +4017,31 @@
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
+        <v>0</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>40.774415059092021</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>80.58943211679366</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>119.40907374805278</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>125.75693062425235</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>155.12982985363337</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>183.61420570954101</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -4013,10 +4080,8 @@
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
-      <c r="N32" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ステップ配信 4通（あいさつメッセージの後、友だち追加から14日以内）</t>
-        </is>
+      <c r="N32" s="69" t="s">
+        <v>187</v>
       </c>
       <c r="O32" s="17" t="s">
         <v>125</v>
@@ -4026,6 +4091,7 @@
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -4043,21 +4109,27 @@
       </c>
       <c r="E33" s="63">
         <f>+E29*E32*$P$26*$P$27*$P$28*$P$36</f>
+        <v>11.369788814554505</v>
       </c>
       <c r="F33" s="63">
         <f t="shared" ref="F33:G33" si="9">+F29*F32*$P$26*$P$27*$P$28*$P$36</f>
+        <v>22.472053186413611</v>
       </c>
       <c r="G33" s="63">
         <f t="shared" si="9"/>
+        <v>33.296760948976249</v>
       </c>
       <c r="H33" s="63">
         <f>+H29*H32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <v>35.066836424070367</v>
       </c>
       <c r="I33" s="63">
         <f t="shared" ref="I33:J33" si="10">+I29*I32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <v>43.257356401493901</v>
       </c>
       <c r="J33" s="63">
         <f t="shared" si="10"/>
+        <v>51.200115053622007</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -4069,6 +4141,7 @@
       </c>
       <c r="Q33" s="73">
         <f t="shared" ref="Q33:Q35" si="11">+IF(P33=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
@@ -4079,24 +4152,31 @@
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
+        <v>0</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E29*E32*$P$28</f>
+        <v>446.30567500000006</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F29*F32*$P$28</f>
+        <v>882.11004000000014</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G29*G32*$P$28</f>
+        <v>1307.0192958750004</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H29*H32*$P$28*$Q$28</f>
+        <v>1376.5012134900005</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I29*I32*$P$28*$Q$28</f>
+        <v>1698.0089922840634</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J29*J32*$P$28*$Q$28</f>
+        <v>2009.7912355093979</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -4108,6 +4188,7 @@
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="11"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
@@ -4118,24 +4199,31 @@
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
+        <v>0</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
+        <v>106.89561794097537</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="12">+F31+F33+1.05*(F31+F33)</f>
+        <v>211.2760448715749</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="12"/>
+        <v>313.04696112890952</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="12"/>
+        <v>329.68872244906157</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="12"/>
+        <v>406.69373182301092</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="12"/>
+        <v>481.36935756448418</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -4147,39 +4235,42 @@
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="11"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="145" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="6" t="str">
         <f>+C8</f>
+        <v>新規応募</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
         <v>0</v>
       </c>
       <c r="E36" s="111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" s="111">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" s="111">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H36" s="111">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I36" s="111">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J36" s="111">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
+        <v>30</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
@@ -4190,13 +4281,15 @@
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
+        <v>1.4641000000000006</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="146"/>
-      <c r="B37" s="6">
+      <c r="B37" s="6" t="str">
         <f>+C9</f>
+        <v>-</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
@@ -4222,6 +4315,7 @@
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
+        <v>0</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
@@ -4232,8 +4326,9 @@
       <c r="A38" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="6" t="str">
         <f>+C10</f>
+        <v>再応募</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -4246,19 +4341,20 @@
         <v>0</v>
       </c>
       <c r="G38" s="111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="111">
         <v>1</v>
       </c>
       <c r="I38" s="111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" s="111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
+        <v>7</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
@@ -4270,8 +4366,9 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="146"/>
-      <c r="B39" s="6">
+      <c r="B39" s="6" t="str">
         <f>+C11</f>
+        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -4297,6 +4394,7 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
+        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
@@ -4314,27 +4412,35 @@
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="13">+SUM(D36:D39)</f>
+        <v>0</v>
       </c>
       <c r="E40" s="10">
         <f t="shared" si="13"/>
+        <v>2</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="13"/>
+        <v>3</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="13"/>
+        <v>6</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="13"/>
+        <v>7</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="13"/>
+        <v>8</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="13"/>
+        <v>11</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
+        <v>37</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -4345,24 +4451,31 @@
       </c>
       <c r="D41" s="18">
         <f t="shared" ref="D41" si="14">+IFERROR(D40/D35,0)</f>
+        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
+        <v>1.8709840857127947E-2</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="15">+IFERROR(F40/F35,0)</f>
+        <v>1.4199432793356026E-2</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="15"/>
+        <v>1.9166453423993667E-2</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="15"/>
+        <v>2.1232148761417012E-2</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="15"/>
+        <v>1.9670821982281057E-2</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="15"/>
+        <v>2.2851475332071675E-2</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>116</v>
@@ -4400,21 +4513,27 @@
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="16">+F75*F76</f>
+        <v>0</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
@@ -4426,27 +4545,35 @@
       <c r="B45" s="138"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
+        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
+        <v>295000</v>
       </c>
       <c r="E45" s="27">
         <f>SUM(E65:E69)+SUM(E71:E72)</f>
+        <v>165000</v>
       </c>
       <c r="F45" s="27">
         <f t="shared" ref="F45:J45" si="17">SUM(F65:F69)+SUM(F71:F72)</f>
+        <v>165000</v>
       </c>
       <c r="G45" s="27">
         <f t="shared" si="17"/>
+        <v>165000</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="17"/>
+        <v>165000</v>
       </c>
       <c r="I45" s="27">
         <f t="shared" si="17"/>
+        <v>165000</v>
       </c>
       <c r="J45" s="27">
         <f t="shared" si="17"/>
+        <v>165000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
@@ -4462,21 +4589,27 @@
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="18">IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
+        <v>365.66866419522893</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="18"/>
+        <v>365.66866419522893</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="18"/>
+        <v>365.66866419522893</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="18"/>
+        <v>365.66866419522893</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="18"/>
+        <v>365.66866419522904</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="18"/>
+        <v>365.66866419522904</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
@@ -4492,21 +4625,27 @@
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="19">+E51/E35</f>
+        <v>1543.5618707130554</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="19"/>
+        <v>780.96880363458149</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="19"/>
+        <v>527.0774691598258</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="19"/>
+        <v>500.47207794768673</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="19"/>
+        <v>405.71070338454678</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
+        <v>342.77212998107512</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
@@ -4522,21 +4661,27 @@
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="20">+SUM(E36:E39)/E35</f>
+        <v>1.8709840857127947E-2</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="20"/>
+        <v>1.4199432793356026E-2</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="20"/>
+        <v>1.9166453423993667E-2</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="20"/>
+        <v>2.1232148761417012E-2</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="20"/>
+        <v>1.9670821982281057E-2</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="20"/>
+        <v>2.2851475332071675E-2</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
@@ -4552,21 +4697,27 @@
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
+        <v>82500</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="21">+IFERROR(F51/SUM(F36:F39),0)</f>
+        <v>55000</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="21"/>
+        <v>27500</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="21"/>
+        <v>23571.428571428572</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="21"/>
+        <v>20625</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="21"/>
+        <v>15000</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
@@ -4582,21 +4733,27 @@
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="F50" s="65">
         <f t="shared" ref="F50:J50" si="22">+F36*$D$8+F38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="G50" s="65">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="H50" s="65">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="I50" s="65">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="J50" s="65">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
@@ -4608,27 +4765,35 @@
       <c r="B51" s="136"/>
       <c r="C51" s="110">
         <f>+C45</f>
+        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
+        <v>295000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
+        <v>165000</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="23">SUM(F45,F50)+F44</f>
+        <v>165000</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="23"/>
+        <v>165000</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="23"/>
+        <v>165000</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="23"/>
+        <v>165000</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
+        <v>165000</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -4658,24 +4823,31 @@
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
+        <v>0</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="24">+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
@@ -4688,24 +4860,31 @@
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
+        <v>295000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
+        <v>165000</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="25">SUM(F65:F72)+F54</f>
+        <v>165000</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="25"/>
+        <v>165000</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="25"/>
+        <v>165000</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="25"/>
+        <v>165000</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="25"/>
+        <v>165000</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
@@ -4721,21 +4900,27 @@
       </c>
       <c r="E56" s="28">
         <f t="shared" ref="E56:J56" si="26">IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
+        <v>365.66866419522893</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" si="26"/>
+        <v>365.66866419522893</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="26"/>
+        <v>365.66866419522893</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="26"/>
+        <v>365.66866419522893</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="26"/>
+        <v>365.66866419522904</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="26"/>
+        <v>365.66866419522904</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
@@ -4751,21 +4936,27 @@
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
+        <v>1543.5618707130554</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="27">+F61/F35</f>
+        <v>780.96880363458149</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="27"/>
+        <v>527.0774691598258</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="27"/>
+        <v>500.47207794768673</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="27"/>
+        <v>405.71070338454678</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="27"/>
+        <v>342.77212998107512</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
@@ -4781,21 +4972,27 @@
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="28">+SUM(E36:E39)/E35</f>
+        <v>1.8709840857127947E-2</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="28"/>
+        <v>1.4199432793356026E-2</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="28"/>
+        <v>1.9166453423993667E-2</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="28"/>
+        <v>2.1232148761417012E-2</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="28"/>
+        <v>1.9670821982281057E-2</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="28"/>
+        <v>2.2851475332071675E-2</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
@@ -4809,21 +5006,27 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
+        <v>82500</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="29">+IFERROR(F55/F40,0)</f>
+        <v>55000</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="29"/>
+        <v>27500</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="29"/>
+        <v>23571.428571428572</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="29"/>
+        <v>20625</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="29"/>
+        <v>15000</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
@@ -4852,24 +5055,31 @@
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
+        <v>295000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
+        <v>165000</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="30">+SUM(F65:F72)+F54</f>
+        <v>165000</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="30"/>
+        <v>165000</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="30"/>
+        <v>165000</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="30"/>
+        <v>165000</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="30"/>
+        <v>165000</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -4946,10 +5156,8 @@
       <c r="J66" s="28">
         <v>30000</v>
       </c>
-      <c r="N66" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ：初期1.5万円・月3万円</t>
-        </is>
+      <c r="N66" s="69" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -4997,21 +5205,27 @@
       </c>
       <c r="E68" s="28">
         <f t="shared" ref="E68:J68" si="31">IF(E34&lt;5000,5000,15000)</f>
+        <v>5000</v>
       </c>
       <c r="F68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="G68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="H68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="I68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="J68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="N68" s="69" t="s">
         <v>176</v>
@@ -5165,24 +5379,31 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
+        <v>295000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="32">SUM(E65:E72)+E54</f>
+        <v>165000</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="32"/>
+        <v>165000</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="32"/>
+        <v>165000</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="32"/>
+        <v>165000</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="32"/>
+        <v>165000</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="32"/>
+        <v>165000</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5203,24 +5424,31 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="33">+IF(D34&lt;30001,0,D34-30000)</f>
+        <v>0</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5229,24 +5457,31 @@
       </c>
       <c r="D76" s="5">
         <f t="shared" ref="D76:J76" si="34">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="G76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="H76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="J76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5342,11 +5577,11 @@
       </c>
       <c r="D4" s="28">
         <f>+SIM!G51</f>
-        <v>135000</v>
+        <v>165000</v>
       </c>
       <c r="E4" s="28">
         <f>+SIM!J51</f>
-        <v>135000</v>
+        <v>165000</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5361,11 +5596,11 @@
       </c>
       <c r="D5" s="28">
         <f>+SIM!G61</f>
-        <v>135000</v>
+        <v>165000</v>
       </c>
       <c r="E5" s="28">
         <f>+SIM!J61</f>
-        <v>135000</v>
+        <v>165000</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5483,11 +5718,11 @@
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
-        <v>431.24520203985747</v>
+        <v>527.0774691598258</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
-        <v>280.44992452997059</v>
+        <v>342.77212998107512</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -5502,11 +5737,11 @@
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
-        <v>431.24520203985747</v>
+        <v>527.0774691598258</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
-        <v>280.44992452997059</v>
+        <v>342.77212998107512</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -5554,11 +5789,11 @@
       </c>
       <c r="D16" s="87">
         <f>SUM(D17:D20)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E16" s="87">
         <f>SUM(E17:E20)</f>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -5582,11 +5817,11 @@
       </c>
       <c r="D17" s="87">
         <f>+SIM!G36</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="87">
         <f>+SIM!J36</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -5663,11 +5898,11 @@
       </c>
       <c r="D19" s="87">
         <f>+SIM!G38</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="87">
         <f>+SIM!J38</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -5724,11 +5959,11 @@
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-        <v>135000</v>
+        <v>27500</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
-        <v>67500</v>
+        <v>15000</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -5748,11 +5983,11 @@
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-        <v>135000</v>
+        <v>27500</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-        <v>67500</v>
+        <v>15000</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>

--- a/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.0.xlsx
+++ b/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46F9FA9-5A61-4A6E-8F93-68881B18DF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB2CCE3-EE2A-4DDF-816D-48B33438F9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
@@ -2947,8 +2947,10 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="56" t="s">
-        <v>178</v>
+      <c r="A4" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">株式会社横浜シミズ御中_LINEOA施策提案【SIM】（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導）</t>
+        </is>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -3037,8 +3039,10 @@
       <c r="K8" s="129">
         <v>0</v>
       </c>
-      <c r="N8" s="69" t="s">
-        <v>180</v>
+      <c r="N8" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CV①新規応募：サイトのLINEボタン・離脱防止で友だちになった方（応募前）が、配信から応募した数。サンクスLINE誘導で友だちになった方は応募済みなので、新規応募には数えない</t>
+        </is>
       </c>
       <c r="O8" s="35" t="s">
         <v>156</v>
@@ -3805,8 +3809,10 @@
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
-      <c r="N26" s="72" t="s">
-        <v>184</v>
+      <c r="N26" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイトのLINEボタン（UUの0.5%・FMTの係数）＋離脱防止ポップアップ＋サンクスLINE誘導</t>
+        </is>
       </c>
       <c r="O26" s="17" t="s">
         <v>40</v>
@@ -4080,8 +4086,10 @@
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
-      <c r="N32" s="69" t="s">
-        <v>187</v>
+      <c r="N32" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ステップ配信 4通（あいさつメッセージの後、友だち追加から14日以内）</t>
+        </is>
       </c>
       <c r="O32" s="17" t="s">
         <v>125</v>
@@ -4254,27 +4262,29 @@
         <v>2</v>
       </c>
       <c r="F36" s="111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" s="111">
+        <v>4</v>
+      </c>
+      <c r="H36" s="111">
         <v>5</v>
       </c>
-      <c r="H36" s="111">
+      <c r="I36" s="111">
+        <v>5</v>
+      </c>
+      <c r="J36" s="111">
         <v>6</v>
-      </c>
-      <c r="I36" s="111">
-        <v>6</v>
-      </c>
-      <c r="J36" s="111">
-        <v>8</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L36" s="7"/>
-      <c r="N36" s="69" t="s">
-        <v>188</v>
+      <c r="N36" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新規応募：サイトのLINEボタン・離脱防止で友だちになった方が、企画配信・ステップ配信から応募した数</t>
+        </is>
       </c>
       <c r="O36" s="17" t="s">
         <v>126</v>
@@ -4344,21 +4354,23 @@
         <v>1</v>
       </c>
       <c r="H38" s="111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" s="111">
         <v>3</v>
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L38" s="7"/>
-      <c r="N38" s="69" t="s">
-        <v>189</v>
+      <c r="N38" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">再応募：一度勤務した方が、次回イベントの募集から勤務希望を出した数（応募→勤務を経てからなので3か月目から）</t>
+        </is>
       </c>
       <c r="O38" s="21" t="s">
         <v>36</v>
@@ -4420,11 +4432,11 @@
       </c>
       <c r="F40" s="10">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="13"/>
@@ -4436,11 +4448,11 @@
       </c>
       <c r="J40" s="10">
         <f t="shared" si="13"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -4459,11 +4471,11 @@
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="15">+IFERROR(F40/F35,0)</f>
-        <v>1.4199432793356026E-2</v>
+        <v>9.4662885289040176E-3</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="15"/>
-        <v>1.9166453423993667E-2</v>
+        <v>1.5972044519994722E-2</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="15"/>
@@ -4475,7 +4487,7 @@
       </c>
       <c r="J41" s="18">
         <f t="shared" si="15"/>
-        <v>2.2851475332071675E-2</v>
+        <v>1.8696661635331371E-2</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>116</v>
@@ -4665,11 +4677,11 @@
       </c>
       <c r="F48" s="32">
         <f t="shared" si="20"/>
-        <v>1.4199432793356026E-2</v>
+        <v>9.4662885289040176E-3</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="20"/>
-        <v>1.9166453423993667E-2</v>
+        <v>1.5972044519994722E-2</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="20"/>
@@ -4681,7 +4693,7 @@
       </c>
       <c r="J48" s="32">
         <f t="shared" si="20"/>
-        <v>2.2851475332071675E-2</v>
+        <v>1.8696661635331371E-2</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
@@ -4701,11 +4713,11 @@
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="21">+IFERROR(F51/SUM(F36:F39),0)</f>
-        <v>55000</v>
+        <v>82500</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="21"/>
-        <v>27500</v>
+        <v>33000</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="21"/>
@@ -4717,7 +4729,7 @@
       </c>
       <c r="J49" s="28">
         <f t="shared" si="21"/>
-        <v>15000</v>
+        <v>18333.333333333332</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
@@ -4976,11 +4988,11 @@
       </c>
       <c r="F58" s="32">
         <f t="shared" si="28"/>
-        <v>1.4199432793356026E-2</v>
+        <v>9.4662885289040176E-3</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="28"/>
-        <v>1.9166453423993667E-2</v>
+        <v>1.5972044519994722E-2</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="28"/>
@@ -4992,7 +5004,7 @@
       </c>
       <c r="J58" s="32">
         <f t="shared" si="28"/>
-        <v>2.2851475332071675E-2</v>
+        <v>1.8696661635331371E-2</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
@@ -5010,11 +5022,11 @@
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="29">+IFERROR(F55/F40,0)</f>
-        <v>55000</v>
+        <v>82500</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="29"/>
-        <v>27500</v>
+        <v>33000</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="29"/>
@@ -5026,7 +5038,7 @@
       </c>
       <c r="J59" s="28">
         <f t="shared" si="29"/>
-        <v>15000</v>
+        <v>18333.333333333332</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
@@ -5156,8 +5168,10 @@
       <c r="J66" s="28">
         <v>30000</v>
       </c>
-      <c r="N66" s="69" t="s">
-        <v>190</v>
+      <c r="N66" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">離脱防止ポップアップ：初期1.5万円・月3万円</t>
+        </is>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5789,11 +5803,11 @@
       </c>
       <c r="D16" s="87">
         <f>SUM(D17:D20)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="87">
         <f>SUM(E17:E20)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -5817,11 +5831,11 @@
       </c>
       <c r="D17" s="87">
         <f>+SIM!G36</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="87">
         <f>+SIM!J36</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -5959,11 +5973,11 @@
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-        <v>27500</v>
+        <v>33000</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
-        <v>15000</v>
+        <v>18333.333333333332</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -5983,11 +5997,11 @@
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-        <v>27500</v>
+        <v>33000</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-        <v>15000</v>
+        <v>18333.333333333332</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>

--- a/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.0.xlsx
+++ b/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB2CCE3-EE2A-4DDF-816D-48B33438F9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D792D9A-6646-4F2E-8CD9-F630B8D9A470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
+    <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
   <sheets>
     <sheet name="SIM" sheetId="1" r:id="rId1"/>
@@ -1526,15 +1526,9 @@
     <t>CV数（+LINEOA施策）</t>
   </si>
   <si>
-    <t>株式会社横浜シミズ御中_LINEOA施策提案【SIM】（サイトのLINEボタン＋サンクスLINE誘導）</t>
-  </si>
-  <si>
     <t>新規応募</t>
   </si>
   <si>
-    <t>CV①新規応募：サイトのLINEボタンで友だちになった方（応募前）が、配信から応募した数。サンクスLINE誘導で友だちになった方は応募済みなので、新規応募には数えない</t>
-  </si>
-  <si>
     <t>再応募</t>
   </si>
   <si>
@@ -1544,27 +1538,12 @@
     <t>サンクスLINE誘導＝応募×遷移80%×追加40%（資料と同じ・定義テキストの係数）</t>
   </si>
   <si>
-    <t>サイトのLINEボタン（UUの0.5%・FMTの係数）＋サンクスLINE誘導。離脱防止は入れていない</t>
-  </si>
-  <si>
     <t>ブロック率：1か月目（E27）から、2か月目以降は前の月×1.025（式）</t>
   </si>
   <si>
     <t>企画配信 月4回（週1回。次回イベントの募集・会場の案内）</t>
   </si>
   <si>
-    <t>ステップ配信は入れていない（資料に無いため）</t>
-  </si>
-  <si>
-    <t>新規応募：合計CVでクリックの0.3〜1.0%前後になるように置く</t>
-  </si>
-  <si>
-    <t>再応募：一度勤務した方が、次回イベントの募集から勤務希望を出した数（応募→勤務を経てからなので4か月目から）</t>
-  </si>
-  <si>
-    <t>離脱防止ポップアップ：入れていない（入れる場合 初期1.5万円・月3万円）</t>
-  </si>
-  <si>
     <t>LINE運用（運用代行・効率改善）</t>
   </si>
   <si>
@@ -1575,6 +1554,27 @@
   </si>
   <si>
     <t>CV③_再応募</t>
+  </si>
+  <si>
+    <t>株式会社横浜シミズ御中_LINEOA施策提案【SIM】（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導）</t>
+  </si>
+  <si>
+    <t>CV①新規応募：サイトのLINEボタン・離脱防止で友だちになった方（応募前）が、配信から応募した数。サンクスLINE誘導で友だちになった方は応募済みなので、新規応募には数えない</t>
+  </si>
+  <si>
+    <t>サイトのLINEボタン（UUの0.5%・FMTの係数）＋離脱防止ポップアップ＋サンクスLINE誘導</t>
+  </si>
+  <si>
+    <t>ステップ配信 4通（あいさつメッセージの後、友だち追加から14日以内）</t>
+  </si>
+  <si>
+    <t>新規応募：サイトのLINEボタン・離脱防止で友だちになった方が、企画配信・ステップ配信から応募した数</t>
+  </si>
+  <si>
+    <t>再応募：一度勤務した方が、次回イベントの募集から勤務希望を出した数（応募→勤務を経てからなので3か月目から）</t>
+  </si>
+  <si>
+    <t>離脱防止ポップアップ：初期1.5万円・月3万円</t>
   </si>
 </sst>
 </file>
@@ -2501,40 +2501,10 @@
     <xf numFmtId="14" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2558,10 +2528,40 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2947,10 +2947,8 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">株式会社横浜シミズ御中_LINEOA施策提案【SIM】（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導）</t>
-        </is>
+      <c r="A4" s="56" t="s">
+        <v>188</v>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -3014,14 +3012,14 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="147" t="s">
+      <c r="A8" s="137" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D8" s="33">
         <v>0</v>
@@ -3039,17 +3037,15 @@
       <c r="K8" s="129">
         <v>0</v>
       </c>
-      <c r="N8" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CV①新規応募：サイトのLINEボタン・離脱防止で友だちになった方（応募前）が、配信から応募した数。サンクスLINE誘導で友だちになった方は応募済みなので、新規応募には数えない</t>
-        </is>
+      <c r="N8" s="69" t="s">
+        <v>189</v>
       </c>
       <c r="O8" s="35" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="148"/>
+      <c r="A9" s="138"/>
       <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
@@ -3079,14 +3075,14 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="147" t="s">
+      <c r="A10" s="137" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D10" s="33">
         <v>0</v>
@@ -3103,11 +3099,11 @@
       <c r="J10" s="29"/>
       <c r="K10" s="118"/>
       <c r="N10" s="132" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="148"/>
+      <c r="A11" s="138"/>
       <c r="B11" s="19" t="s">
         <v>10</v>
       </c>
@@ -3141,10 +3137,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="149" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="149"/>
+      <c r="A13" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="139"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>28</v>
@@ -3187,7 +3183,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="150" t="s">
+      <c r="A14" s="140" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -3229,7 +3225,7 @@
       </c>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="151"/>
+      <c r="A15" s="141"/>
       <c r="B15" s="20" t="s">
         <v>34</v>
       </c>
@@ -3278,7 +3274,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="152"/>
+      <c r="A16" s="142"/>
       <c r="B16" s="20" t="s">
         <v>151</v>
       </c>
@@ -3327,7 +3323,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="150" t="s">
+      <c r="A17" s="140" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -3372,7 +3368,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="151"/>
+      <c r="A18" s="141"/>
       <c r="B18" s="8" t="s">
         <v>172</v>
       </c>
@@ -3436,7 +3432,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="151"/>
+      <c r="A19" s="141"/>
       <c r="B19" s="8" t="s">
         <v>114</v>
       </c>
@@ -3497,7 +3493,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="151"/>
+      <c r="A20" s="141"/>
       <c r="B20" s="8" t="s">
         <v>112</v>
       </c>
@@ -3532,7 +3528,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="152"/>
+      <c r="A21" s="142"/>
       <c r="B21" s="8" t="s">
         <v>113</v>
       </c>
@@ -3575,7 +3571,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="153" t="s">
+      <c r="A22" s="143" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3621,7 +3617,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="151"/>
+      <c r="A23" s="141"/>
       <c r="B23" s="6" t="s">
         <v>172</v>
       </c>
@@ -3674,7 +3670,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="151"/>
+      <c r="A24" s="141"/>
       <c r="B24" s="6" t="s">
         <v>114</v>
       </c>
@@ -3709,7 +3705,7 @@
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
       <c r="N24" s="69" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O24" s="22" t="s">
         <v>43</v>
@@ -3727,7 +3723,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="152"/>
+      <c r="A25" s="142"/>
       <c r="B25" s="6" t="s">
         <v>67</v>
       </c>
@@ -3775,10 +3771,10 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="137" t="s">
+      <c r="A26" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="138"/>
+      <c r="B26" s="145"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>20</v>
@@ -3809,10 +3805,8 @@
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
-      <c r="N26" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトのLINEボタン（UUの0.5%・FMTの係数）＋離脱防止ポップアップ＋サンクスLINE誘導</t>
-        </is>
+      <c r="N26" s="72" t="s">
+        <v>190</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>40</v>
@@ -3827,10 +3821,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="137" t="s">
+      <c r="A27" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="138"/>
+      <c r="B27" s="145"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0</v>
@@ -3861,7 +3855,7 @@
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
       <c r="N27" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O27" s="17" t="s">
         <v>41</v>
@@ -3879,10 +3873,10 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="154" t="s">
+      <c r="A28" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="155"/>
+      <c r="B28" s="147"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>0</v>
@@ -3929,10 +3923,10 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="143" t="s">
+      <c r="A29" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="144"/>
+      <c r="B29" s="149"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
@@ -3974,10 +3968,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="141" t="s">
+      <c r="A30" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="142"/>
+      <c r="B30" s="136"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -4003,7 +3997,7 @@
       <c r="K30" s="11"/>
       <c r="L30" s="7"/>
       <c r="N30" s="69" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O30" s="17" t="s">
         <v>120</v>
@@ -4016,10 +4010,10 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="137" t="s">
+      <c r="A31" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="138"/>
+      <c r="B31" s="145"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
@@ -4058,10 +4052,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="141" t="s">
+      <c r="A32" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="142"/>
+      <c r="B32" s="136"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -4086,10 +4080,8 @@
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
-      <c r="N32" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ステップ配信 4通（あいさつメッセージの後、友だち追加から14日以内）</t>
-        </is>
+      <c r="N32" s="69" t="s">
+        <v>191</v>
       </c>
       <c r="O32" s="17" t="s">
         <v>125</v>
@@ -4107,10 +4099,10 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="137" t="s">
+      <c r="A33" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="138"/>
+      <c r="B33" s="145"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
@@ -4153,10 +4145,10 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="143" t="s">
+      <c r="A34" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="144"/>
+      <c r="B34" s="149"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
@@ -4200,10 +4192,10 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="143" t="s">
+      <c r="A35" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="144"/>
+      <c r="B35" s="149"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
@@ -4247,7 +4239,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="145" t="s">
+      <c r="A36" s="150" t="s">
         <v>5</v>
       </c>
       <c r="B36" s="6" t="str">
@@ -4281,10 +4273,8 @@
         <v>24</v>
       </c>
       <c r="L36" s="7"/>
-      <c r="N36" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">新規応募：サイトのLINEボタン・離脱防止で友だちになった方が、企画配信・ステップ配信から応募した数</t>
-        </is>
+      <c r="N36" s="69" t="s">
+        <v>192</v>
       </c>
       <c r="O36" s="17" t="s">
         <v>126</v>
@@ -4296,7 +4286,7 @@
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="146"/>
+      <c r="A37" s="151"/>
       <c r="B37" s="6" t="str">
         <f>+C9</f>
         <v>-</v>
@@ -4333,7 +4323,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="145" t="s">
+      <c r="A38" s="150" t="s">
         <v>8</v>
       </c>
       <c r="B38" s="6" t="str">
@@ -4367,17 +4357,15 @@
         <v>9</v>
       </c>
       <c r="L38" s="7"/>
-      <c r="N38" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">再応募：一度勤務した方が、次回イベントの募集から勤務希望を出した数（応募→勤務を経てからなので3か月目から）</t>
-        </is>
+      <c r="N38" s="69" t="s">
+        <v>193</v>
       </c>
       <c r="O38" s="21" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="146"/>
+      <c r="A39" s="151"/>
       <c r="B39" s="6" t="str">
         <f>+C11</f>
         <v>-</v>
@@ -4417,10 +4405,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="139" t="s">
+      <c r="A40" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="140"/>
+      <c r="B40" s="153"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="13">+SUM(D36:D39)</f>
@@ -4515,10 +4503,10 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="137" t="s">
+      <c r="A44" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="138"/>
+      <c r="B44" s="145"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>21</v>
@@ -4551,10 +4539,10 @@
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="137" t="s">
+      <c r="A45" s="144" t="s">
         <v>131</v>
       </c>
-      <c r="B45" s="138"/>
+      <c r="B45" s="145"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
         <v>0</v>
@@ -4565,36 +4553,36 @@
       </c>
       <c r="E45" s="27">
         <f>SUM(E65:E69)+SUM(E71:E72)</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="F45" s="27">
         <f t="shared" ref="F45:J45" si="17">SUM(F65:F69)+SUM(F71:F72)</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="G45" s="27">
         <f t="shared" si="17"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="17"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="I45" s="27">
         <f t="shared" si="17"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="J45" s="27">
         <f t="shared" si="17"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="137" t="s">
+      <c r="A46" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="138"/>
+      <c r="B46" s="145"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>21</v>
@@ -4627,46 +4615,46 @@
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="137" t="s">
+      <c r="A47" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="138"/>
+      <c r="B47" s="145"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="19">+E51/E35</f>
-        <v>1543.5618707130554</v>
+        <v>2011.3078921412541</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="19"/>
-        <v>780.96880363458149</v>
+        <v>1017.6260168571819</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="19"/>
-        <v>527.0774691598258</v>
+        <v>686.79791435977302</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="19"/>
-        <v>500.47207794768673</v>
+        <v>652.13028338637969</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="19"/>
-        <v>405.71070338454678</v>
+        <v>528.65334077380339</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
-        <v>342.77212998107512</v>
+        <v>446.64247239958274</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="137" t="s">
+      <c r="A48" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="138"/>
+      <c r="B48" s="145"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>21</v>
@@ -4699,46 +4687,46 @@
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="139" t="s">
+      <c r="A49" s="152" t="s">
         <v>18</v>
       </c>
-      <c r="B49" s="140"/>
+      <c r="B49" s="153"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
-        <v>82500</v>
+        <v>107500</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="21">+IFERROR(F51/SUM(F36:F39),0)</f>
-        <v>82500</v>
+        <v>107500</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="21"/>
-        <v>33000</v>
+        <v>43000</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="21"/>
-        <v>23571.428571428572</v>
+        <v>30714.285714285714</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="21"/>
-        <v>20625</v>
+        <v>26875</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="21"/>
-        <v>18333.333333333332</v>
+        <v>23888.888888888891</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="139" t="s">
+      <c r="A50" s="152" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="140"/>
+      <c r="B50" s="153"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>21</v>
@@ -4771,10 +4759,10 @@
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="135" t="s">
+      <c r="A51" s="154" t="s">
         <v>68</v>
       </c>
-      <c r="B51" s="136"/>
+      <c r="B51" s="155"/>
       <c r="C51" s="110">
         <f>+C45</f>
         <v>0</v>
@@ -4785,27 +4773,27 @@
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="23">SUM(F45,F50)+F44</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="23"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="23"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="23"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -4828,10 +4816,10 @@
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="137" t="s">
+      <c r="A54" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B54" s="138"/>
+      <c r="B54" s="145"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
@@ -4865,10 +4853,10 @@
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="137" t="s">
+      <c r="A55" s="144" t="s">
         <v>131</v>
       </c>
-      <c r="B55" s="138"/>
+      <c r="B55" s="145"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
@@ -4876,36 +4864,36 @@
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="25">SUM(F65:F72)+F54</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="25"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="25"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="25"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="25"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="137" t="s">
+      <c r="A56" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="B56" s="138"/>
+      <c r="B56" s="145"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>21</v>
@@ -4938,46 +4926,46 @@
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="137" t="s">
+      <c r="A57" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="138"/>
+      <c r="B57" s="145"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
-        <v>1543.5618707130554</v>
+        <v>2011.3078921412541</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="27">+F61/F35</f>
-        <v>780.96880363458149</v>
+        <v>1017.6260168571819</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="27"/>
-        <v>527.0774691598258</v>
+        <v>686.79791435977302</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="27"/>
-        <v>500.47207794768673</v>
+        <v>652.13028338637969</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="27"/>
-        <v>405.71070338454678</v>
+        <v>528.65334077380339</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="27"/>
-        <v>342.77212998107512</v>
+        <v>446.64247239958274</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="137" t="s">
+      <c r="A58" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="B58" s="138"/>
+      <c r="B58" s="145"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>21</v>
@@ -5010,44 +4998,44 @@
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="139" t="s">
+      <c r="A59" s="152" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="140"/>
+      <c r="B59" s="153"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
-        <v>82500</v>
+        <v>107500</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="29">+IFERROR(F55/F40,0)</f>
-        <v>82500</v>
+        <v>107500</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="29"/>
-        <v>33000</v>
+        <v>43000</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="29"/>
-        <v>23571.428571428572</v>
+        <v>30714.285714285714</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="29"/>
-        <v>20625</v>
+        <v>26875</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="29"/>
-        <v>18333.333333333332</v>
+        <v>23888.888888888891</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="139" t="s">
+      <c r="A60" s="152" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="140"/>
+      <c r="B60" s="153"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -5060,10 +5048,10 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="135" t="s">
+      <c r="A61" s="154" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="136"/>
+      <c r="B61" s="155"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
@@ -5071,27 +5059,27 @@
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="30">+SUM(F65:F72)+F54</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="30"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="30"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="30"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="30"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -5168,10 +5156,8 @@
       <c r="J66" s="28">
         <v>30000</v>
       </c>
-      <c r="N66" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ：初期1.5万円・月3万円</t>
-        </is>
+      <c r="N66" s="69" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5254,7 +5240,7 @@
     <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="15"/>
       <c r="B69" s="6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C69" s="90">
         <v>0</v>
@@ -5263,25 +5249,25 @@
         <v>100000</v>
       </c>
       <c r="E69" s="28">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="F69" s="28">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="G69" s="28">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="H69" s="28">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I69" s="28">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="J69" s="28">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="N69" s="69" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O69" s="5" t="s">
         <v>51</v>
@@ -5397,27 +5383,27 @@
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="32">SUM(E65:E72)+E54</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="32"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="32"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="32"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="32"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="32"/>
-        <v>165000</v>
+        <v>215000</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5500,17 +5486,18 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
@@ -5523,18 +5510,17 @@
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5591,11 +5577,11 @@
       </c>
       <c r="D4" s="28">
         <f>+SIM!G51</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="E4" s="28">
         <f>+SIM!J51</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5610,11 +5596,11 @@
       </c>
       <c r="D5" s="28">
         <f>+SIM!G61</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="E5" s="28">
         <f>+SIM!J61</f>
-        <v>165000</v>
+        <v>215000</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5732,11 +5718,11 @@
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
-        <v>527.0774691598258</v>
+        <v>686.79791435977302</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
-        <v>342.77212998107512</v>
+        <v>446.64247239958274</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -5751,11 +5737,11 @@
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
-        <v>527.0774691598258</v>
+        <v>686.79791435977302</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
-        <v>342.77212998107512</v>
+        <v>446.64247239958274</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -5822,7 +5808,7 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="85" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
@@ -5903,7 +5889,7 @@
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="85" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
@@ -5973,11 +5959,11 @@
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-        <v>33000</v>
+        <v>43000</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
-        <v>18333.333333333332</v>
+        <v>23888.888888888891</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -5997,11 +5983,11 @@
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-        <v>33000</v>
+        <v>43000</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-        <v>18333.333333333332</v>
+        <v>23888.888888888891</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -6687,20 +6673,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6722,6 +6708,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -6735,12 +6729,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>